--- a/spec_crews/datadog_monitoring_v2.xlsx
+++ b/spec_crews/datadog_monitoring_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jochungi/WORK/DEV/meta_ai_generator/spec_crews/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970019ED-D61B-1F4C-89F0-2B635453AA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE3D42C-E329-EB45-AD38-1077D02E2C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="51">
   <si>
     <t>task_name</t>
   </si>
@@ -332,15 +332,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Datadog Logs API를 사용하여 {time_range} 시간 범위 동안 {datadog_query} 쿼리와 일치하는 애플리케이션 로그를 가져옵니다. 최대 {limit}개의 로그 이벤트를 가져옵니다. 반환된 데이터에 타임스탬프, 로그 레벨, 메시지, 서비스 이름 및 스택 트레이스가 포함되도록 합니다.  Datadog 로그 검색 API 요청을 아래와 같이 구성합니다.  조회 옵션은 {seach_option} 에 따라 다르게 호출합니다. 데이터 0건 시 임의 생성 금지 및 "조회 결과 없음" 을 분명히 명시합니다.
-    - apm : APM 트레이스 엔드포인트: ~/api/v2/spans/events/search
-    - logs : 로그 검색 엔드포인트: ~/api/v2/logs/events/search
-    - 인증 헤더(DD-API-KEY 및 DD-APPLICATION-KEY)에 DD_API_KEY 및 DD_APP_KEY를 사용합니다.
-    - 쿼리 및 시간 범위를 본문(body) 매개변수로 포함하여 POST 요청을 제출합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">당신은 프로덕션 인시던트를 진단한 다년간의 경험을 가진 노련한 사이트 신뢰성 엔지니어(SRE)입니다. 로그 데이터를 구문 분석하고, 오류 급증을 포착하며, 스택 트레이스를 식별하고, 경고와 심각한 오류를 분류하며, 엔지니어링 팀이 신속하게 조치할 수 있도록 돕는 의미 있는 패턴을 찾아내는 데 탁월합니다. 가상 데이터를 활용하여 데이터 생성하는 것을 거부합니다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Datadog Logs API를 사용하여 {time_range} 시간 범위 동안 {datadog_query} 쿼리와 일치하는 애플리케이션 로그를 가져옵니다. 최대 {limit}개의 로그 이벤트를 가져옵니다. 반환된 데이터에 타임스탬프, 로그 레벨, 메시지, 서비스 이름 및 스택 트레이스가 포함되도록 합니다.  Datadog 로그 검색 API 요청을 아래와 같이 구성합니다.  조회 옵션(search_option) 은 {seach_option} 이고,  여기에 맞게 Tool 을 호출합니다. 데이터 0건 시 임의 생성 금지 및 "조회 결과 없음" 을 분명히 명시합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Datadog에서 가져온 원본 로그 데이터를 분석합니다. 분석에는 다음 내용이 포함되어야 합니다:  이전에 추출된 정보 이외에 임의적인 데이터 추론 및 분석을 하면 안됩니다.
+    - 심각한 오류 및 예외 식별 및 분류
+    - 경고 및 이상 징후 강조
+    - 반복되는 오류 패턴 또는 급증 감지
+    - 스택 트레이스 또는 근본 원인 지표 기록
+    - 오류 발생 빈도 및 영향을 받는 서비스 요약
+    - {time_range} 시간 범위 동안의 트렌드 파악</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -907,7 +913,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>26</v>
@@ -938,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>29</v>
@@ -954,7 +960,7 @@
         <v>47</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>

--- a/spec_crews/datadog_monitoring_v2.xlsx
+++ b/spec_crews/datadog_monitoring_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jochungi/WORK/DEV/meta_ai_generator/spec_crews/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE3D42C-E329-EB45-AD38-1077D02E2C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D26B9E-6F2A-3247-A22C-C5A273A7AF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -309,34 +309,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>생성된 로그 분석 보고서를 Microsoft Outlook (또는 Google Gmail)을 통해 {recipient_email}로 전송합니다.
-    - 제목 : 애플리케이션 로그 모니터링 보고서 ({time_range})
-    - 전체 마크다운 보고서를 이메일 본문에 포함합니다(가능한 경우 HTML로 서식 지정). 
-    - 이메일이 성공적으로 전송되었는지 확인하고 전달을 확정합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>로그 모니터링 보고서가 포함된 이메일이 메일 서버를 통해 {recipient_email}로 성공적으로 전송되었다는 확인(Confirmation) 메시지입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모니터링 보고서의 제목, 세부정보를   메일 서버를 통해서 전송합니다.  이때 SendOutLookMail 툴에 제목, 내용, 수신자{recipient_email} 정보를 전달해야 합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{time_range} 시간 범위 동안 {datadog_query} 쿼리를 기반으로 API를 사용하여 Datadog에서 애플리케이션 로그를 가져오고, 분석을 위해 원본(raw) 로그 데이터를 반환합니다. Custom_tool 을 호출할때는 {seach_option} 에 따라서 다르게 호출되도록 해당 파라미터를 전달합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>원본 애플리케이션 로그를 분석하여 심각한 오류, 예외, 이상 징후 및 반복되는 패턴을 식별하고, 인사이트와 근본 원인 가설을 포함한 구조화된 분석 결과를 생성합니다.  이때 앞단계에서 가져온 정보 외에 임의로 분석 데이터를 추가하지 말아야 합니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">당신은 프로덕션 인시던트를 진단한 다년간의 경험을 가진 노련한 사이트 신뢰성 엔지니어(SRE)입니다. 로그 데이터를 구문 분석하고, 오류 급증을 포착하며, 스택 트레이스를 식별하고, 경고와 심각한 오류를 분류하며, 엔지니어링 팀이 신속하게 조치할 수 있도록 돕는 의미 있는 패턴을 찾아내는 데 탁월합니다. 가상 데이터를 활용하여 데이터 생성하는 것을 거부합니다. </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Datadog Logs API를 사용하여 {time_range} 시간 범위 동안 {datadog_query} 쿼리와 일치하는 애플리케이션 로그를 가져옵니다. 최대 {limit}개의 로그 이벤트를 가져옵니다. 반환된 데이터에 타임스탬프, 로그 레벨, 메시지, 서비스 이름 및 스택 트레이스가 포함되도록 합니다.  Datadog 로그 검색 API 요청을 아래와 같이 구성합니다.  조회 옵션(search_option) 은 {seach_option} 이고,  여기에 맞게 Tool 을 호출합니다. 데이터 0건 시 임의 생성 금지 및 "조회 결과 없음" 을 분명히 명시합니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -347,6 +324,29 @@
     - 스택 트레이스 또는 근본 원인 지표 기록
     - 오류 발생 빈도 및 영향을 받는 서비스 요약
     - {time_range} 시간 범위 동안의 트렌드 파악</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Datadog Logs API를 사용하여 {time_range} 시간 범위 동안 {datadog_query} 쿼리와 일치하는 애플리케이션 로그를 가져옵니다. 최대 {limit}개의 로그 이벤트를 가져옵니다. 반환된 데이터에 타임스탬프, 로그 레벨, 메시지, 서비스 이름 및 스택 트레이스가 포함되도록 합니다.  Datadog 로그 검색 API 요청을 아래와 같이 구성합니다.  조회 옵션(search_option) 은 {search_option} 이고,  여기에 맞게 Tool 을 호출합니다. 데이터 0건 시 임의 생성 금지 및 "조회 결과 없음" 을 분명히 명시합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{time_range} 시간 범위 동안 {datadog_query} 쿼리를 기반으로 API를 사용하여 Datadog에서 애플리케이션 로그를 가져오고, 분석을 위해 원본(raw) 로그 데이터를 반환합니다. Custom_tool 을 호출할때는 search_option 에 따라서 다르게 호출되도록 해당 파라미터를 전달합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">생성된 로그 분석 보고서를 SendOutLookMail 도구를 호출 하여 전송합니다.
+    - 제목 : 애플리케이션 로그 모니터링 보고서 ({time_range})
+    - 본문 : 전체 마크다운 보고서 (가능한 경우 HTML로 서식 지정). 
+    - 이메일이 성공적으로 전송되었는지 확인하고 전달을 확정합니다.  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그 모니터링 보고서가 포함된 이메일이 메일 서버를 통해  성공적으로 전송되었다는 확인(Confirmation) 메시지입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모니터링 보고서의 제목, 세부정보를   메일 서버를 통해서 전송합니다.  이때 SendOutLookMail 툴에 제목, 내용, 수신자 정보를 전달해야 합니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -913,7 +913,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>26</v>
@@ -926,7 +926,7 @@
         <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>16</v>
@@ -944,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>29</v>
@@ -957,10 +957,10 @@
         <v>17</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
@@ -996,7 +996,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="139" customHeight="1">
+    <row r="5" spans="1:11" ht="131" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
@@ -1004,10 +1004,10 @@
         <v>10</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="8" t="s">
@@ -1017,7 +1017,7 @@
         <v>23</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>25</v>
